--- a/tools/matrices/stride-threats.xlsx
+++ b/tools/matrices/stride-threats.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Serafin\Desktop\analisis_riesgos_api_gateway\tools\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Serafin\Desktop\2026\Clases\ISI\ISI - Trabajo Final\analisis_riesgos_api_gateway\tools\matrices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3400EA14-C864-4F42-A99B-A31F9953122F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E44E30-1DA0-4817-AB15-0981C4F90F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4FF2D350-6023-460C-9AC4-5A075D5155A3}"/>
   </bookViews>
   <sheets>
     <sheet name="stride-threats" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="132">
   <si>
     <t>ID</t>
   </si>
@@ -169,9 +169,6 @@
     <t>CWE-345</t>
   </si>
   <si>
-    <t>C06</t>
-  </si>
-  <si>
     <t>TH08</t>
   </si>
   <si>
@@ -383,6 +380,42 @@
   </si>
   <si>
     <t>CWE-266</t>
+  </si>
+  <si>
+    <t>C02, C04</t>
+  </si>
+  <si>
+    <t>C09</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>C06, C07</t>
+  </si>
+  <si>
+    <t>C03, C12</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>C08</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>C01, C11</t>
+  </si>
+  <si>
+    <t>C11</t>
   </si>
 </sst>
 </file>
@@ -868,7 +901,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -925,6 +960,90 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="CuadroTexto 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E777586-B0CD-EC8C-E597-5049A1B92B13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13192126" y="5543550"/>
+          <a:ext cx="1838324" cy="971550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="38100" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-UY" sz="1100"/>
+            <a:t>Nota: el control de mitigación </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-UY" sz="1100"/>
+            <a:t>"C11" se aplica ante todas las amenazas. Por simplicidad no se agrega a todos los elementos de la columna.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1257,7 +1376,8 @@
     <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="18.28515625" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="13" max="13" width="17.140625" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1339,7 +1459,7 @@
         <v>18</v>
       </c>
       <c r="M2" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -1380,7 +1500,7 @@
         <v>18</v>
       </c>
       <c r="M3" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -1421,7 +1541,7 @@
         <v>18</v>
       </c>
       <c r="M4" t="s">
-        <v>29</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -1585,24 +1705,24 @@
         <v>18</v>
       </c>
       <c r="M8" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
         <v>50</v>
-      </c>
-      <c r="B9" t="s">
-        <v>51</v>
       </c>
       <c r="C9" t="s">
         <v>36</v>
       </c>
       <c r="D9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" t="s">
         <v>52</v>
-      </c>
-      <c r="E9" t="s">
-        <v>53</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -1631,19 +1751,19 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
         <v>54</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
       </c>
       <c r="C10" t="s">
         <v>36</v>
       </c>
       <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
         <v>56</v>
-      </c>
-      <c r="E10" t="s">
-        <v>57</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -1667,24 +1787,24 @@
         <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
         <v>60</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>61</v>
-      </c>
-      <c r="E11" t="s">
-        <v>62</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -1708,24 +1828,24 @@
         <v>18</v>
       </c>
       <c r="M11" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
         <v>63</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
         <v>64</v>
       </c>
-      <c r="C12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>65</v>
-      </c>
-      <c r="E12" t="s">
-        <v>66</v>
       </c>
       <c r="F12">
         <v>7</v>
@@ -1749,24 +1869,24 @@
         <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
         <v>67</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
         <v>68</v>
       </c>
-      <c r="C13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>69</v>
-      </c>
-      <c r="E13" t="s">
-        <v>70</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -1790,24 +1910,24 @@
         <v>34</v>
       </c>
       <c r="M13" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
       <c r="C14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" t="s">
         <v>72</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>73</v>
-      </c>
-      <c r="E14" t="s">
-        <v>74</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -1831,24 +1951,24 @@
         <v>18</v>
       </c>
       <c r="M14" t="s">
-        <v>39</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" t="s">
         <v>75</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" t="s">
         <v>76</v>
       </c>
-      <c r="C15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>77</v>
-      </c>
-      <c r="E15" t="s">
-        <v>78</v>
       </c>
       <c r="F15">
         <v>10</v>
@@ -1877,19 +1997,19 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" t="s">
         <v>80</v>
-      </c>
-      <c r="E16" t="s">
-        <v>81</v>
       </c>
       <c r="F16">
         <v>7</v>
@@ -1913,24 +2033,24 @@
         <v>34</v>
       </c>
       <c r="M16" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" t="s">
         <v>82</v>
       </c>
-      <c r="B17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>83</v>
-      </c>
-      <c r="E17" t="s">
-        <v>84</v>
       </c>
       <c r="F17">
         <v>10</v>
@@ -1959,19 +2079,19 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" t="s">
         <v>85</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" t="s">
         <v>86</v>
       </c>
-      <c r="C18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" t="s">
-        <v>87</v>
-      </c>
       <c r="E18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18">
         <v>4</v>
@@ -1995,24 +2115,24 @@
         <v>18</v>
       </c>
       <c r="M18" t="s">
-        <v>39</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
       <c r="C19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" t="s">
         <v>89</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>90</v>
-      </c>
-      <c r="E19" t="s">
-        <v>91</v>
       </c>
       <c r="F19">
         <v>9</v>
@@ -2036,24 +2156,24 @@
         <v>44</v>
       </c>
       <c r="M19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" t="s">
         <v>93</v>
       </c>
-      <c r="B20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>94</v>
-      </c>
-      <c r="E20" t="s">
-        <v>95</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -2077,24 +2197,24 @@
         <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" t="s">
         <v>97</v>
-      </c>
-      <c r="E21" t="s">
-        <v>98</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -2118,24 +2238,24 @@
         <v>18</v>
       </c>
       <c r="M21" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B22" t="s">
         <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22">
         <v>7</v>
@@ -2159,24 +2279,24 @@
         <v>18</v>
       </c>
       <c r="M22" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" t="s">
         <v>101</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" t="s">
         <v>102</v>
       </c>
-      <c r="C23" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" t="s">
-        <v>103</v>
-      </c>
       <c r="E23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F23">
         <v>8</v>
@@ -2200,24 +2320,24 @@
         <v>34</v>
       </c>
       <c r="M23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
       </c>
       <c r="C24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" t="s">
         <v>105</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>106</v>
-      </c>
-      <c r="E24" t="s">
-        <v>107</v>
       </c>
       <c r="F24">
         <v>9</v>
@@ -2246,19 +2366,19 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" t="s">
         <v>108</v>
       </c>
-      <c r="B25" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" t="s">
-        <v>105</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>109</v>
-      </c>
-      <c r="E25" t="s">
-        <v>110</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -2282,24 +2402,24 @@
         <v>18</v>
       </c>
       <c r="M25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" t="s">
         <v>111</v>
       </c>
-      <c r="B26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>112</v>
-      </c>
-      <c r="E26" t="s">
-        <v>113</v>
       </c>
       <c r="F26">
         <v>7</v>
@@ -2328,19 +2448,19 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B27" t="s">
         <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" t="s">
         <v>115</v>
-      </c>
-      <c r="E27" t="s">
-        <v>116</v>
       </c>
       <c r="F27">
         <v>8</v>
@@ -2364,24 +2484,24 @@
         <v>18</v>
       </c>
       <c r="M27" t="s">
-        <v>58</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B28" t="s">
         <v>117</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" t="s">
         <v>118</v>
       </c>
-      <c r="C28" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>119</v>
-      </c>
-      <c r="E28" t="s">
-        <v>120</v>
       </c>
       <c r="F28">
         <v>7</v>
@@ -2405,10 +2525,11 @@
         <v>18</v>
       </c>
       <c r="M28" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>